--- a/outputs/monitor_xlsx/20260414.xlsx
+++ b/outputs/monitor_xlsx/20260414.xlsx
@@ -544,10 +544,6 @@
           <t>+2.37%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+0.78%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+2.60%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>-0.86%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+2.35%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.40%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+2.04%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>-3.97%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>-8.85%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>689.08億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>462.18億</t>
@@ -811,7 +774,6 @@
           <t>-59.98億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>3.66億</t>
@@ -822,8 +784,6 @@
           <t>18.28億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>165.4%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>136.05%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>684.31億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>12028口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>10061口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-66.12億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-57.04億</t>
@@ -1019,10 +965,6 @@
           <t>None億</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1179,6 +1121,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1299,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1307,20 +1250,23 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>3.1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>129128</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>65981</v>
       </c>
       <c r="H4" t="n">
-        <v>230744</v>
+        <v>296726</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>-984</v>
@@ -1332,11 +1278,14 @@
         <v>8969</v>
       </c>
       <c r="M4" t="n">
-        <v>40626</v>
+        <v>49595</v>
       </c>
       <c r="N4" t="n">
         <v>-4606094</v>
       </c>
+      <c r="O4" t="n">
+        <v>8.529999999999999</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1359,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>830</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1.59</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>2361</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>62</v>
       </c>
       <c r="H5" t="n">
-        <v>-814</v>
+        <v>-753</v>
       </c>
       <c r="I5" t="n">
         <v>32</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="K5" t="n">
         <v>26</v>
@@ -1387,11 +1336,14 @@
         <v>2679</v>
       </c>
       <c r="M5" t="n">
-        <v>10734</v>
+        <v>13413</v>
       </c>
       <c r="N5" t="n">
         <v>-78969</v>
       </c>
+      <c r="O5" t="n">
+        <v>-3.29</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1414,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1750</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0.57</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>12801</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>-2178</v>
       </c>
       <c r="H6" t="n">
-        <v>5298</v>
+        <v>3119</v>
       </c>
       <c r="I6" t="n">
         <v>-159</v>
       </c>
       <c r="J6" t="n">
-        <v>-416</v>
+        <v>-575</v>
       </c>
       <c r="K6" t="n">
         <v>227</v>
@@ -1442,11 +1394,14 @@
         <v>5020</v>
       </c>
       <c r="M6" t="n">
-        <v>20259</v>
+        <v>25279</v>
       </c>
       <c r="N6" t="n">
         <v>-649292</v>
       </c>
+      <c r="O6" t="n">
+        <v>15.07</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1469,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>2055</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>3.27</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>46188</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>18955</v>
       </c>
       <c r="H7" t="n">
-        <v>26000</v>
+        <v>44955</v>
       </c>
       <c r="I7" t="n">
         <v>615</v>
       </c>
       <c r="J7" t="n">
-        <v>-4651</v>
+        <v>-4036</v>
       </c>
       <c r="K7" t="n">
         <v>848</v>
@@ -1497,11 +1452,14 @@
         <v>27299</v>
       </c>
       <c r="M7" t="n">
-        <v>108791</v>
+        <v>136090</v>
       </c>
       <c r="N7" t="n">
         <v>-6483060</v>
       </c>
+      <c r="O7" t="n">
+        <v>9.75</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1524,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1890</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>3.85</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>4059</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>-142</v>
       </c>
       <c r="H8" t="n">
-        <v>-471</v>
+        <v>-613</v>
       </c>
       <c r="I8" t="n">
         <v>196</v>
       </c>
       <c r="J8" t="n">
-        <v>697</v>
+        <v>893</v>
       </c>
       <c r="K8" t="n">
         <v>76</v>
@@ -1552,11 +1510,14 @@
         <v>1502</v>
       </c>
       <c r="M8" t="n">
-        <v>6835</v>
+        <v>8337</v>
       </c>
       <c r="N8" t="n">
         <v>-140253</v>
       </c>
+      <c r="O8" t="n">
+        <v>15.54</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1579,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1840</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>-2.13</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>3470</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>-831</v>
       </c>
       <c r="H9" t="n">
-        <v>-1657</v>
+        <v>-2488</v>
       </c>
       <c r="I9" t="n">
         <v>72</v>
       </c>
       <c r="J9" t="n">
-        <v>1218</v>
+        <v>1290</v>
       </c>
       <c r="K9" t="n">
         <v>85</v>
@@ -1607,11 +1568,14 @@
         <v>1955</v>
       </c>
       <c r="M9" t="n">
-        <v>7948</v>
+        <v>9903</v>
       </c>
       <c r="N9" t="n">
         <v>-106304</v>
       </c>
+      <c r="O9" t="n">
+        <v>13.51</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1634,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>3605</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>8.42</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>3407</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>491</v>
       </c>
       <c r="H10" t="n">
-        <v>212</v>
+        <v>702</v>
       </c>
       <c r="I10" t="n">
         <v>-73</v>
       </c>
       <c r="J10" t="n">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="K10" t="n">
         <v>79</v>
@@ -1662,11 +1626,14 @@
         <v>1843</v>
       </c>
       <c r="M10" t="n">
-        <v>7586</v>
+        <v>9429</v>
       </c>
       <c r="N10" t="n">
         <v>-89536</v>
       </c>
+      <c r="O10" t="n">
+        <v>23.21</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1689,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>2075</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>-6.95</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>4265</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>-792</v>
       </c>
       <c r="H11" t="n">
-        <v>-370</v>
+        <v>-1162</v>
       </c>
       <c r="I11" t="n">
         <v>-283</v>
       </c>
       <c r="J11" t="n">
-        <v>-201</v>
+        <v>-484</v>
       </c>
       <c r="K11" t="n">
         <v>219</v>
@@ -1717,11 +1684,14 @@
         <v>4144</v>
       </c>
       <c r="M11" t="n">
-        <v>15601</v>
+        <v>19745</v>
       </c>
       <c r="N11" t="n">
         <v>-19572</v>
       </c>
+      <c r="O11" t="n">
+        <v>2.74</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1744,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>8470</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>-1.05</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>359</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>-27</v>
       </c>
       <c r="H12" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
         <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="K12" t="n">
         <v>33</v>
@@ -1772,11 +1742,14 @@
         <v>287</v>
       </c>
       <c r="M12" t="n">
-        <v>1248</v>
+        <v>1535</v>
       </c>
       <c r="N12" t="n">
         <v>-9010</v>
       </c>
+      <c r="O12" t="n">
+        <v>11.22</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1799,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2175</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>-6.25</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4529</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>-508</v>
       </c>
       <c r="H13" t="n">
-        <v>77</v>
+        <v>-431</v>
       </c>
       <c r="I13" t="n">
         <v>-409</v>
       </c>
       <c r="J13" t="n">
-        <v>-241</v>
+        <v>-650</v>
       </c>
       <c r="K13" t="n">
         <v>104</v>
@@ -1827,11 +1800,14 @@
         <v>159</v>
       </c>
       <c r="M13" t="n">
-        <v>-42</v>
+        <v>117</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1854,26 +1830,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>485</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>25514</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>-579</v>
       </c>
       <c r="H14" t="n">
-        <v>31</v>
+        <v>-548</v>
       </c>
       <c r="I14" t="n">
         <v>-6</v>
       </c>
       <c r="J14" t="n">
-        <v>-636</v>
+        <v>-642</v>
       </c>
       <c r="K14" t="n">
         <v>-73</v>
@@ -1882,11 +1858,14 @@
         <v>1972</v>
       </c>
       <c r="M14" t="n">
-        <v>-741</v>
+        <v>1231</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1909,26 +1888,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>1035</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="F15" t="n">
-        <v>880</v>
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>-222</v>
       </c>
       <c r="H15" t="n">
-        <v>-95</v>
+        <v>-317</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>23</v>
@@ -1937,11 +1916,14 @@
         <v>17</v>
       </c>
       <c r="M15" t="n">
-        <v>-154</v>
+        <v>-137</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1964,26 +1946,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1755</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1470</v>
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>-48</v>
       </c>
       <c r="H16" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="I16" t="n">
         <v>109</v>
       </c>
       <c r="J16" t="n">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="K16" t="n">
         <v>-16</v>
@@ -1992,11 +1974,14 @@
         <v>-182</v>
       </c>
       <c r="M16" t="n">
-        <v>282</v>
+        <v>100</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2019,26 +2004,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="6" t="n">
         <v>672</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="7" t="n">
         <v>961</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>204</v>
       </c>
       <c r="H17" t="n">
-        <v>327</v>
+        <v>531</v>
       </c>
       <c r="I17" t="n">
         <v>15</v>
       </c>
       <c r="J17" t="n">
-        <v>-93</v>
+        <v>-78</v>
       </c>
       <c r="K17" t="n">
         <v>57</v>
@@ -2047,10 +2032,13 @@
         <v>9211</v>
       </c>
       <c r="M17" t="n">
-        <v>39174</v>
+        <v>48385</v>
       </c>
       <c r="N17" t="n">
         <v>-21799</v>
+      </c>
+      <c r="O17" t="n">
+        <v>56.04</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>

--- a/outputs/monitor_xlsx/20260414.xlsx
+++ b/outputs/monitor_xlsx/20260414.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2046,165 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1720</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12902</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>121</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1689</v>
+      </c>
+      <c r="I18" t="n">
+        <v>143</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-892</v>
+      </c>
+      <c r="K18" t="n">
+        <v>415</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7296</v>
+      </c>
+      <c r="M18" t="n">
+        <v>33333</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400947</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>597</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10850</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-19589</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-2224</v>
+      </c>
+      <c r="J19" t="n">
+        <v>30375</v>
+      </c>
+      <c r="K19" t="n">
+        <v>221</v>
+      </c>
+      <c r="L19" t="n">
+        <v>35232</v>
+      </c>
+      <c r="M19" t="n">
+        <v>175270</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393653</v>
+      </c>
+      <c r="O19" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>646</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="F20" t="n">
+        <v>14865</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-1281</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-5230</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-74</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2473</v>
+      </c>
+      <c r="K20" t="n">
+        <v>766</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8160</v>
+      </c>
+      <c r="M20" t="n">
+        <v>42247</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161063</v>
+      </c>
+      <c r="O20" t="n">
+        <v>11.23</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
